--- a/out/Attention-Mamba1_repeat_3_000002.xlsx
+++ b/out/Attention-Mamba1_repeat_3_000002.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-2.967222099549092</v>
+        <v>15.28973846592426</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.434846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.434846904977811</v>
+        <v>0.1742763026941591</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.034846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.034846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>1.034846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.034846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.034846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.034846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-2.967222099549092</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>0.434846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.434846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.034846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.034846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.034846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.034846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.034846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.034846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.034846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.434846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.434846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.434846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.434846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.434846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.434846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.434846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.434846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.434846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.434846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.434846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.434846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.434846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.434846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.434846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.434846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.434846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.434846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.434846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.434846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.434846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.434846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,14 +35122,14 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.434846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35917,14 +35917,14 @@
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.434846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36712,14 +36712,14 @@
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.434846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37507,14 +37507,14 @@
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA46" t="n">
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-2.967222099549092</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38306,10 +38306,10 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.434846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39101,10 +39101,10 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.434846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39896,10 +39896,10 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.034846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40691,10 +40691,10 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.034846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41486,10 +41486,10 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.034846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42281,10 +42281,10 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>1.034846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43076,10 +43076,10 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.034846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43867,14 +43867,14 @@
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA54" t="n">
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-2.967222099549092</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44662,14 +44662,14 @@
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA55" t="n">
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-2.967222099549092</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45461,10 +45461,10 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.434846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46252,14 +46252,14 @@
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA57" t="n">
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-2.967222099549092</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47051,10 +47051,10 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.434846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47846,10 +47846,10 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.434846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48637,14 +48637,14 @@
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA60" t="n">
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-2.367222099549092</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49436,10 +49436,10 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>1.034846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50231,10 +50231,10 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.034846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51022,14 +51022,14 @@
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA63" t="n">
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-2.367222099549092</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51817,14 +51817,14 @@
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA64" t="n">
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-2.967222099549092</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52616,10 +52616,10 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.434846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53411,10 +53411,10 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.034846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54206,10 +54206,10 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.034846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -55001,10 +55001,10 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>1.034846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55792,14 +55792,14 @@
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA69" t="n">
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-2.367222099549092</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56587,14 +56587,14 @@
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA70" t="n">
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-2.967222099549092</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57382,14 +57382,14 @@
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA71" t="n">
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-2.967222099549092</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58177,14 +58177,14 @@
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA72" t="n">
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-2.967222099549092</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58972,14 +58972,14 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA73" t="n">
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-2.967222099549092</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59771,10 +59771,10 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.434846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60562,14 +60562,14 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA75" t="n">
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-2.967222099549092</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61357,14 +61357,14 @@
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA76" t="n">
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-2.367222099549092</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62152,14 +62152,14 @@
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA77" t="n">
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-2.967222099549092</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62947,14 +62947,14 @@
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA78" t="n">
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-2.967222099549092</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63742,14 +63742,14 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA79" t="n">
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-2.967222099549092</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64537,14 +64537,14 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA80" t="n">
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-2.967222099549092</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65336,10 +65336,10 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>1.034846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66131,10 +66131,10 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>1.034846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66926,10 +66926,10 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.034846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67717,14 +67717,14 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA84" t="n">
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-2.367222099549092</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68516,10 +68516,10 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.034846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69307,14 +69307,14 @@
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA86" t="n">
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-2.967222099549092</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70102,14 +70102,14 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA87" t="n">
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-2.967222099549092</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70901,10 +70901,10 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.434846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71696,10 +71696,10 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>1.034846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72491,10 +72491,10 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>1.034846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73282,14 +73282,14 @@
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA91" t="n">
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-2.367222099549092</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74081,10 +74081,10 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>1.034846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74876,10 +74876,10 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>1.034846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75667,14 +75667,14 @@
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA94" t="n">
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-2.367222099549092</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76462,14 +76462,14 @@
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA95" t="n">
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-2.967222099549092</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77261,10 +77261,10 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.434846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78056,10 +78056,10 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.434846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78847,14 +78847,14 @@
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA98" t="n">
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-2.367222099549092</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79646,10 +79646,10 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>1.034846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80441,10 +80441,10 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.034846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81236,10 +81236,10 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>1.034846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82031,10 +82031,10 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>1.034846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82826,10 +82826,10 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>1.034846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83621,10 +83621,10 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>1.034846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84416,10 +84416,10 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>1.034846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85211,10 +85211,10 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>1.034846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86006,10 +86006,10 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>1.034846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86801,10 +86801,10 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.434846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87596,10 +87596,10 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.434846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88391,10 +88391,10 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.434846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89186,10 +89186,10 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.434846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89981,10 +89981,10 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.434846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90776,10 +90776,10 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.434846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91571,10 +91571,10 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.434846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92366,10 +92366,10 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.434846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93161,10 +93161,10 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.434846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93956,10 +93956,10 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.434846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94751,10 +94751,10 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.434846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95546,10 +95546,10 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.434846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96341,10 +96341,10 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.434846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97136,10 +97136,10 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.434846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97931,10 +97931,10 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.434846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98726,10 +98726,10 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.434846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99521,10 +99521,10 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.434846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100316,10 +100316,10 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.434846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101111,10 +101111,10 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.434846904977811</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/Attention-Mamba1_repeat_3_000002.xlsx
+++ b/out/Attention-Mamba1_repeat_3_000002.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-2.967222099549092</v>
+        <v>-0.702528638138725</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.434846904977811</v>
+        <v>-0.3137207519070789</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.434846904977811</v>
+        <v>0.4638950205562133</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.034846904977811</v>
+        <v>0.6638950205562134</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.034846904977811</v>
+        <v>0.6638950205562134</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>1.034846904977811</v>
+        <v>0.6638950205562134</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.034846904977811</v>
+        <v>0.6638950205562134</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.034846904977811</v>
+        <v>0.6638950205562134</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA10" t="n">
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.034846904977811</v>
+        <v>-0.1137207519070789</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-2.967222099549092</v>
+        <v>-0.3137207519070788</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA12" t="n">
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>0.434846904977811</v>
+        <v>-0.3137207519070788</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.434846904977811</v>
+        <v>0.4638950205562133</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.034846904977811</v>
+        <v>0.4638950205562133</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.034846904977811</v>
+        <v>0.6638950205562134</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.034846904977811</v>
+        <v>0.6638950205562134</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.034846904977811</v>
+        <v>0.6638950205562134</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.034846904977811</v>
+        <v>0.6638950205562134</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.034846904977811</v>
+        <v>0.6638950205562134</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.034846904977811</v>
+        <v>0.6638950205562134</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.434846904977811</v>
+        <v>0.6638950205562134</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.434846904977811</v>
+        <v>0.4638950205562133</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.434846904977811</v>
+        <v>0.4638950205562133</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.434846904977811</v>
+        <v>0.4638950205562133</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.434846904977811</v>
+        <v>0.4638950205562133</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.434846904977811</v>
+        <v>0.4638950205562133</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.434846904977811</v>
+        <v>0.4638950205562133</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.434846904977811</v>
+        <v>0.4638950205562133</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.434846904977811</v>
+        <v>0.4638950205562133</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.434846904977811</v>
+        <v>0.4638950205562133</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.434846904977811</v>
+        <v>0.4638950205562133</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.434846904977811</v>
+        <v>0.4638950205562133</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.434846904977811</v>
+        <v>0.4638950205562133</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.434846904977811</v>
+        <v>0.4638950205562133</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.434846904977811</v>
+        <v>0.4638950205562133</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.434846904977811</v>
+        <v>0.4638950205562133</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.434846904977811</v>
+        <v>0.4638950205562133</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.434846904977811</v>
+        <v>0.4638950205562133</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.434846904977811</v>
+        <v>0.4638950205562133</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.434846904977811</v>
+        <v>0.4638950205562133</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.434846904977811</v>
+        <v>0.4638950205562133</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.434846904977811</v>
+        <v>0.4638950205562133</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.434846904977811</v>
+        <v>0.4638950205562133</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.434846904977811</v>
+        <v>0.4638950205562133</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,7 +36719,7 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.434846904977811</v>
+        <v>-0.3137207519070789</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37507,14 +37507,14 @@
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA46" t="n">
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-2.967222099549092</v>
+        <v>-0.313720751907079</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38309,7 +38309,7 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.434846904977811</v>
+        <v>-0.313720751907079</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39104,7 +39104,7 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.434846904977811</v>
+        <v>0.4638950205562133</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39899,7 +39899,7 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.034846904977811</v>
+        <v>0.4638950205562133</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40694,7 +40694,7 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.034846904977811</v>
+        <v>0.6638950205562134</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41489,7 +41489,7 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.034846904977811</v>
+        <v>0.6638950205562134</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42284,7 +42284,7 @@
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>1.034846904977811</v>
+        <v>0.6638950205562134</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43079,7 +43079,7 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.034846904977811</v>
+        <v>-0.1137207519070789</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43867,14 +43867,14 @@
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA54" t="n">
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-2.967222099549092</v>
+        <v>-1.091336524370371</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44662,14 +44662,14 @@
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA55" t="n">
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-2.967222099549092</v>
+        <v>-1.091336524370371</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45464,7 +45464,7 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.434846904977811</v>
+        <v>-1.091336524370371</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46252,14 +46252,14 @@
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA57" t="n">
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-2.967222099549092</v>
+        <v>-0.3137207519070789</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47054,7 +47054,7 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.434846904977811</v>
+        <v>-0.3137207519070789</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47849,7 +47849,7 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.434846904977811</v>
+        <v>-0.3137207519070789</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48637,14 +48637,14 @@
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA60" t="n">
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-2.367222099549092</v>
+        <v>-0.1137207519070788</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49439,7 +49439,7 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>1.034846904977811</v>
+        <v>-0.1137207519070788</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50234,7 +50234,7 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.034846904977811</v>
+        <v>-0.1137207519070789</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51022,14 +51022,14 @@
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA63" t="n">
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-2.367222099549092</v>
+        <v>-0.8913365243703711</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51817,14 +51817,14 @@
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA64" t="n">
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-2.967222099549092</v>
+        <v>-1.091336524370371</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52619,7 +52619,7 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.434846904977811</v>
+        <v>-0.3137207519070789</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53414,7 +53414,7 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.034846904977811</v>
+        <v>0.6638950205562134</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54209,7 +54209,7 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.034846904977811</v>
+        <v>0.6638950205562134</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -55004,7 +55004,7 @@
         <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>1.034846904977811</v>
+        <v>-0.1137207519070789</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55792,14 +55792,14 @@
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA69" t="n">
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-2.367222099549092</v>
+        <v>-0.8913365243703711</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56594,7 +56594,7 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-2.967222099549092</v>
+        <v>-1.868952296833664</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57389,7 +57389,7 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-2.967222099549092</v>
+        <v>-1.868952296833664</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58184,7 +58184,7 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-2.967222099549092</v>
+        <v>-1.868952296833664</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58972,14 +58972,14 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA73" t="n">
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-2.967222099549092</v>
+        <v>-1.091336524370371</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59774,7 +59774,7 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.434846904977811</v>
+        <v>-1.091336524370371</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60562,14 +60562,14 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA75" t="n">
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-2.967222099549092</v>
+        <v>-1.091336524370371</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61364,7 +61364,7 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-2.367222099549092</v>
+        <v>-1.868952296833664</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62159,7 +62159,7 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-2.967222099549092</v>
+        <v>-1.868952296833664</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62954,7 +62954,7 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-2.967222099549092</v>
+        <v>-1.868952296833664</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63749,7 +63749,7 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-2.967222099549092</v>
+        <v>-1.868952296833664</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64537,14 +64537,14 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA80" t="n">
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-2.967222099549092</v>
+        <v>-1.091336524370371</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65339,7 +65339,7 @@
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>1.034846904977811</v>
+        <v>-0.1137207519070789</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66134,7 +66134,7 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>1.034846904977811</v>
+        <v>0.6638950205562134</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66929,7 +66929,7 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.034846904977811</v>
+        <v>-0.1137207519070789</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67717,14 +67717,14 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA84" t="n">
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-2.367222099549092</v>
+        <v>-0.1137207519070789</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68519,7 +68519,7 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.034846904977811</v>
+        <v>-0.8913365243703711</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69307,14 +69307,14 @@
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA86" t="n">
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-2.967222099549092</v>
+        <v>-0.8913365243703711</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70102,14 +70102,14 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA87" t="n">
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-2.967222099549092</v>
+        <v>-1.091336524370371</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70904,7 +70904,7 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.434846904977811</v>
+        <v>-0.3137207519070789</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71699,7 +71699,7 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>1.034846904977811</v>
+        <v>0.6638950205562134</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72494,7 +72494,7 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>1.034846904977811</v>
+        <v>-0.1137207519070789</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73282,14 +73282,14 @@
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA91" t="n">
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-2.367222099549092</v>
+        <v>-0.1137207519070789</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74084,7 +74084,7 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>1.034846904977811</v>
+        <v>-0.1137207519070789</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74879,7 +74879,7 @@
         <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>1.034846904977811</v>
+        <v>-0.1137207519070789</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75667,14 +75667,14 @@
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA94" t="n">
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-2.367222099549092</v>
+        <v>-1.091336524370371</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76462,14 +76462,14 @@
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA95" t="n">
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-2.967222099549092</v>
+        <v>-1.091336524370371</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77264,7 +77264,7 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.434846904977811</v>
+        <v>-0.3137207519070789</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78059,7 +78059,7 @@
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.434846904977811</v>
+        <v>-0.3137207519070789</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78847,14 +78847,14 @@
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA98" t="n">
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-2.367222099549092</v>
+        <v>-0.1137207519070788</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79649,7 +79649,7 @@
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>1.034846904977811</v>
+        <v>-0.1137207519070788</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80444,7 +80444,7 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.034846904977811</v>
+        <v>0.6638950205562134</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81239,7 +81239,7 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>1.034846904977811</v>
+        <v>0.6638950205562134</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82034,7 +82034,7 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>1.034846904977811</v>
+        <v>0.6638950205562134</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82829,7 +82829,7 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>1.034846904977811</v>
+        <v>0.6638950205562134</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83624,7 +83624,7 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>1.034846904977811</v>
+        <v>0.6638950205562134</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84419,7 +84419,7 @@
         <v>1</v>
       </c>
       <c r="JB105" t="n">
-        <v>1.034846904977811</v>
+        <v>0.6638950205562134</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85214,7 +85214,7 @@
         <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>1.034846904977811</v>
+        <v>0.6638950205562134</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86009,7 +86009,7 @@
         <v>1</v>
       </c>
       <c r="JB107" t="n">
-        <v>1.034846904977811</v>
+        <v>0.6638950205562134</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86804,7 +86804,7 @@
         <v>1</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.434846904977811</v>
+        <v>0.6638950205562134</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87599,7 +87599,7 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.434846904977811</v>
+        <v>0.4638950205562133</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88394,7 +88394,7 @@
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.434846904977811</v>
+        <v>0.4638950205562133</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89189,7 +89189,7 @@
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.434846904977811</v>
+        <v>0.4638950205562133</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89984,7 +89984,7 @@
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.434846904977811</v>
+        <v>0.4638950205562133</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90779,7 +90779,7 @@
         <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.434846904977811</v>
+        <v>0.4638950205562133</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91574,7 +91574,7 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.434846904977811</v>
+        <v>0.4638950205562133</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92369,7 +92369,7 @@
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.434846904977811</v>
+        <v>0.4638950205562133</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93164,7 +93164,7 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.434846904977811</v>
+        <v>0.4638950205562133</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93959,7 +93959,7 @@
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.434846904977811</v>
+        <v>0.4638950205562133</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94754,7 +94754,7 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.434846904977811</v>
+        <v>0.4638950205562133</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95549,7 +95549,7 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.434846904977811</v>
+        <v>0.4638950205562133</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96344,7 +96344,7 @@
         <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.434846904977811</v>
+        <v>0.4638950205562133</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97139,7 +97139,7 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.434846904977811</v>
+        <v>0.4638950205562133</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97934,7 +97934,7 @@
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.434846904977811</v>
+        <v>0.4638950205562133</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98729,7 +98729,7 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.434846904977811</v>
+        <v>0.4638950205562133</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99524,7 +99524,7 @@
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.434846904977811</v>
+        <v>0.4638950205562133</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100319,7 +100319,7 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.434846904977811</v>
+        <v>0.4638950205562133</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101114,7 +101114,7 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.434846904977811</v>
+        <v>0.4638950205562133</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/Attention-Mamba1_repeat_3_000002.xlsx
+++ b/out/Attention-Mamba1_repeat_3_000002.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.0001116208732128143</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.702528638138725</v>
+        <v>-0.72</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.002363406121730804</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.3137207519070789</v>
+        <v>-0.7899999999999999</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.0004736483097076416</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.4638950205562133</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.001206707209348679</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.6638950205562134</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.001806978136301041</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.6638950205562134</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0.001470096409320831</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.6638950205562134</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0.001550443470478058</v>
       </c>
       <c r="JB8" t="n">
-        <v>0.6638950205562134</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0.00305546447634697</v>
       </c>
       <c r="JB9" t="n">
-        <v>0.6638950205562134</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.005070902407169342</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.1137207519070789</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.0004217624664306641</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.3137207519070788</v>
+        <v>0.16</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.000566776841878891</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.3137207519070788</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0.001259185373783112</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.4638950205562133</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.002088837325572968</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.4638950205562133</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.001273643225431442</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.6638950205562134</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.001709435135126114</v>
       </c>
       <c r="JB16" t="n">
-        <v>0.6638950205562134</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.001599088311195374</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.6638950205562134</v>
+        <v>0.16</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.001685433089733124</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.6638950205562134</v>
+        <v>0.3</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.001693606376647949</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.6638950205562134</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.001878924667835236</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.6638950205562134</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.002373587340116501</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.6638950205562134</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.001747835427522659</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.4638950205562133</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.001978680491447449</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.4638950205562133</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.002917341887950897</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.4638950205562133</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.006828833371400833</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.4638950205562133</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.0007895193994045258</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.4638950205562133</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.001827914267778397</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.4638950205562133</v>
+        <v>-0.3</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.001864012330770493</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.4638950205562133</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.001822631806135178</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.4638950205562133</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.00147688016295433</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.4638950205562133</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.001843106001615524</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.4638950205562133</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.002026986330747604</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.4638950205562133</v>
+        <v>-0.3</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.002251844853162766</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.4638950205562133</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.002403635531663895</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.4638950205562133</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.002477541565895081</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.4638950205562133</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.003094639629125595</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.4638950205562133</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.004314795136451721</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.4638950205562133</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.001914806663990021</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.4638950205562133</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.001821074634790421</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.4638950205562133</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.005018271505832672</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.4638950205562133</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.006204992532730103</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.4638950205562133</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.01270582899451256</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.4638950205562133</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.0229528620839119</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.4638950205562133</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.01511051878333092</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.4638950205562133</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,10 +36716,10 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.07352101802825928</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.3137207519070789</v>
+        <v>-0.16</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37511,10 +37511,10 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.0005749836564064026</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.313720751907079</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38306,10 +38306,10 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.004277411848306656</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.313720751907079</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39101,10 +39101,10 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.001026410609483719</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.4638950205562133</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39896,10 +39896,10 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.004037041217088699</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.4638950205562133</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40691,10 +40691,10 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.0006199963390827179</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.6638950205562134</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41486,10 +41486,10 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.01639550924301147</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.6638950205562134</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42281,10 +42281,10 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0.003963802009820938</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.6638950205562134</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43076,10 +43076,10 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.003281161189079285</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.1137207519070789</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43871,10 +43871,10 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.0008365362882614136</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.091336524370371</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44666,10 +44666,10 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.0005563609302043915</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.091336524370371</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45461,10 +45461,10 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.001211550086736679</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.091336524370371</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46256,10 +46256,10 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.001406852155923843</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.3137207519070789</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47051,10 +47051,10 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.000127844512462616</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.3137207519070789</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47846,10 +47846,10 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.002312362194061279</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.3137207519070789</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48641,10 +48641,10 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.0001480728387832642</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.1137207519070788</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49436,10 +49436,10 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.0004664324223995209</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.1137207519070788</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50231,10 +50231,10 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.003625638782978058</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.1137207519070789</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51026,10 +51026,10 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.000569462776184082</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.8913365243703711</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51821,10 +51821,10 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.0007309019565582275</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.091336524370371</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52616,10 +52616,10 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.002870101481676102</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.3137207519070789</v>
+        <v>0.16</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53411,10 +53411,10 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.005549635738134384</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.6638950205562134</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54206,10 +54206,10 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.01030046120285988</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.6638950205562134</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -55001,10 +55001,10 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0.001795757561922073</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.1137207519070789</v>
+        <v>0.16</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55796,10 +55796,10 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.001280978322029114</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.8913365243703711</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56587,14 +56587,14 @@
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.0006418265402317047</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.868952296833664</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57382,14 +57382,14 @@
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.0004691779613494873</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.868952296833664</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58177,14 +58177,14 @@
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.0003867931663990021</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.868952296833664</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58976,10 +58976,10 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.001154553145170212</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.091336524370371</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59771,10 +59771,10 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.0002450048923492432</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.091336524370371</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60566,10 +60566,10 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.0007973648607730865</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.091336524370371</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61357,14 +61357,14 @@
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.0006425864994525909</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.868952296833664</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62152,14 +62152,14 @@
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.0002654120326042175</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.868952296833664</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62947,14 +62947,14 @@
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.0004202574491500854</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.868952296833664</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63742,14 +63742,14 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.0003372132778167725</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.868952296833664</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64541,10 +64541,10 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-4.739686846733093e-05</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.091336524370371</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65336,10 +65336,10 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0.0002598240971565247</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.1137207519070789</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66131,10 +66131,10 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.0002559274435043335</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.6638950205562134</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66926,10 +66926,10 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.00052604079246521</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.1137207519070789</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67721,10 +67721,10 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-5.774199962615967e-05</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.1137207519070789</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68516,10 +68516,10 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>9.954348206520081e-05</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.8913365243703711</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69311,10 +69311,10 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.0005376860499382019</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.8913365243703711</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70106,10 +70106,10 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-4.968792200088501e-05</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.091336524370371</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70901,10 +70901,10 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.0007690638303756714</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.3137207519070789</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71696,10 +71696,10 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.0001666992902755737</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.6638950205562134</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72491,10 +72491,10 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.001778941601514816</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.1137207519070789</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73286,10 +73286,10 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.0008808821439743042</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.1137207519070789</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74081,10 +74081,10 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>4.189461469650269e-05</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.1137207519070789</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74876,10 +74876,10 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>7.845461368560791e-06</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.1137207519070789</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75671,10 +75671,10 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.0008180961012840271</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.091336524370371</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76466,10 +76466,10 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.0001852698624134064</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.091336524370371</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77261,10 +77261,10 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.0004197321832180023</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.3137207519070789</v>
+        <v>0.16</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78056,10 +78056,10 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0.0007252171635627747</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.3137207519070789</v>
+        <v>0.3</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78851,10 +78851,10 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.0001263730227947235</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.1137207519070788</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79646,10 +79646,10 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0.0001699179410934448</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.1137207519070788</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80441,10 +80441,10 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.0006348639726638794</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.6638950205562134</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81236,10 +81236,10 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.0005564466118812561</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.6638950205562134</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82031,10 +82031,10 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.0003828033804893494</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.6638950205562134</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82826,10 +82826,10 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.001070313155651093</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.6638950205562134</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83621,10 +83621,10 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0.0005764737725257874</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.6638950205562134</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84416,10 +84416,10 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0.0005468837916851044</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.6638950205562134</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85211,10 +85211,10 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0.0007580257952213287</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.6638950205562134</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86006,10 +86006,10 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0.0006873011589050293</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.6638950205562134</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86801,10 +86801,10 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0.0009616166353225708</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.6638950205562134</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87596,10 +87596,10 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.001348711550235748</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.4638950205562133</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88391,10 +88391,10 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0.001130864024162292</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.4638950205562133</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89186,10 +89186,10 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.00135393813252449</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.4638950205562133</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89981,10 +89981,10 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.001111045479774475</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.4638950205562133</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90776,10 +90776,10 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0.001405570656061172</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.4638950205562133</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91571,10 +91571,10 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.001741401851177216</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.4638950205562133</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92366,10 +92366,10 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.001216951757669449</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.4638950205562133</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93161,10 +93161,10 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.001905921846628189</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.4638950205562133</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93956,10 +93956,10 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.004883572459220886</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.4638950205562133</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94751,10 +94751,10 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.003376524895429611</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.4638950205562133</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95546,10 +95546,10 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.01440791413187981</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.4638950205562133</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96341,10 +96341,10 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0.0008019618690013885</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.4638950205562133</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97136,10 +97136,10 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.007012870162725449</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.4638950205562133</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97931,10 +97931,10 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0.0002719983458518982</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.4638950205562133</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98726,10 +98726,10 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.0008075572550296783</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.4638950205562133</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99521,10 +99521,10 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0.001770146191120148</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.4638950205562133</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100316,10 +100316,10 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.001041524112224579</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.4638950205562133</v>
+        <v>-0.5799999999999996</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101111,10 +101111,10 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.005076412111520767</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.4638950205562133</v>
+        <v>-0.4399999999999996</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/Attention-Mamba1_repeat_3_000002.xlsx
+++ b/out/Attention-Mamba1_repeat_3_000002.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>-0.0001116208732128143</v>
+        <v>-0.0001116320490837097</v>
       </c>
       <c r="JB2" t="n">
         <v>-0.72</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0.002363406121730804</v>
+        <v>0.002363398671150208</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.7899999999999999</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0.0004736483097076416</v>
+        <v>0.0004736185073852539</v>
       </c>
       <c r="JB4" t="n">
         <v>-0.8599999999999999</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0.001806978136301041</v>
+        <v>0.001806993037462234</v>
       </c>
       <c r="JB6" t="n">
         <v>-0.9999999999999998</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0.001470096409320831</v>
+        <v>0.001470074057579041</v>
       </c>
       <c r="JB7" t="n">
         <v>-0.7199999999999999</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0.001550443470478058</v>
+        <v>0.001550417393445969</v>
       </c>
       <c r="JB8" t="n">
         <v>-0.4399999999999999</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0.00305546447634697</v>
+        <v>0.003055460751056671</v>
       </c>
       <c r="JB9" t="n">
         <v>-0.4399999999999999</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0.005070902407169342</v>
+        <v>0.005070909857749939</v>
       </c>
       <c r="JB10" t="n">
         <v>-0.4399999999999999</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>-0.0004217624664306641</v>
+        <v>-0.0004217661917209625</v>
       </c>
       <c r="JB11" t="n">
         <v>0.16</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0.000566776841878891</v>
+        <v>0.0005667842924594879</v>
       </c>
       <c r="JB12" t="n">
         <v>-0.1199999999999999</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0.001259185373783112</v>
+        <v>0.00125918909907341</v>
       </c>
       <c r="JB13" t="n">
         <v>-0.9999999999999998</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0.002088837325572968</v>
+        <v>0.002088826149702072</v>
       </c>
       <c r="JB14" t="n">
         <v>-0.8599999999999999</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0.001273643225431442</v>
+        <v>0.001273602247238159</v>
       </c>
       <c r="JB15" t="n">
         <v>-0.7199999999999999</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0.001709435135126114</v>
+        <v>0.001709457486867905</v>
       </c>
       <c r="JB16" t="n">
         <v>-0.5799999999999998</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0.001599088311195374</v>
+        <v>0.001599062234163284</v>
       </c>
       <c r="JB17" t="n">
         <v>0.16</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0.001685433089733124</v>
+        <v>0.001685421913862228</v>
       </c>
       <c r="JB18" t="n">
         <v>0.3</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0.002373587340116501</v>
+        <v>0.002373583614826202</v>
       </c>
       <c r="JB21" t="n">
         <v>0.4399999999999999</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0.001747835427522659</v>
+        <v>0.001747842878103256</v>
       </c>
       <c r="JB22" t="n">
         <v>0.5799999999999998</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0.001978680491447449</v>
+        <v>0.001978687942028046</v>
       </c>
       <c r="JB23" t="n">
         <v>0.7199999999999999</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0.002917341887950897</v>
+        <v>0.002917364239692688</v>
       </c>
       <c r="JB24" t="n">
         <v>0.4399999999999999</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0.006828833371400833</v>
+        <v>0.006828837096691132</v>
       </c>
       <c r="JB25" t="n">
         <v>0.4399999999999999</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0.0007895193994045258</v>
+        <v>0.0007895156741142273</v>
       </c>
       <c r="JB26" t="n">
         <v>-0.1600000000000001</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0.001827914267778397</v>
+        <v>0.00182792916893959</v>
       </c>
       <c r="JB27" t="n">
         <v>-0.3</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0.001864012330770493</v>
+        <v>0.001864045858383179</v>
       </c>
       <c r="JB28" t="n">
         <v>-0.5799999999999998</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0.001822631806135178</v>
+        <v>0.001822628080844879</v>
       </c>
       <c r="JB29" t="n">
         <v>-0.4399999999999999</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0.00147688016295433</v>
+        <v>0.001476895064115524</v>
       </c>
       <c r="JB30" t="n">
         <v>-0.4399999999999999</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0.001843106001615524</v>
+        <v>0.001843094825744629</v>
       </c>
       <c r="JB31" t="n">
         <v>-0.4399999999999999</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0.002026986330747604</v>
+        <v>0.002026975154876709</v>
       </c>
       <c r="JB32" t="n">
         <v>-0.3</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0.002251844853162766</v>
+        <v>0.002251852303743362</v>
       </c>
       <c r="JB33" t="n">
         <v>0.5799999999999998</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0.002403635531663895</v>
+        <v>0.002403620630502701</v>
       </c>
       <c r="JB34" t="n">
         <v>0.7199999999999999</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0.002477541565895081</v>
+        <v>0.002477526664733887</v>
       </c>
       <c r="JB35" t="n">
         <v>0.8599999999999999</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0.003094639629125595</v>
+        <v>0.003094635903835297</v>
       </c>
       <c r="JB36" t="n">
         <v>0.8599999999999999</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0.004314795136451721</v>
+        <v>0.004314817488193512</v>
       </c>
       <c r="JB37" t="n">
         <v>0.7199999999999999</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0.001914806663990021</v>
+        <v>0.001914858818054199</v>
       </c>
       <c r="JB38" t="n">
         <v>0.7199999999999999</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0.001821074634790421</v>
+        <v>0.001821082085371017</v>
       </c>
       <c r="JB39" t="n">
         <v>0.7199999999999999</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0.005018271505832672</v>
+        <v>0.005018282681703568</v>
       </c>
       <c r="JB40" t="n">
         <v>0.7199999999999999</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0.006204992532730103</v>
+        <v>0.006204951554536819</v>
       </c>
       <c r="JB41" t="n">
         <v>0.8599999999999999</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0.01270582899451256</v>
+        <v>0.01270583271980286</v>
       </c>
       <c r="JB42" t="n">
         <v>0.9999999999999998</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0.0229528620839119</v>
+        <v>0.02295288443565369</v>
       </c>
       <c r="JB43" t="n">
         <v>0.9999999999999998</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0.01511051878333092</v>
+        <v>0.01511053740978241</v>
       </c>
       <c r="JB44" t="n">
         <v>0.7199999999999999</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0.07352101802825928</v>
+        <v>0.07352102547883987</v>
       </c>
       <c r="JB45" t="n">
         <v>-0.16</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>-0.0005749836564064026</v>
+        <v>-0.0005749799311161041</v>
       </c>
       <c r="JB46" t="n">
         <v>-0.4399999999999999</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0.004277411848306656</v>
+        <v>0.004277389496564865</v>
       </c>
       <c r="JB47" t="n">
         <v>-0.7199999999999999</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0.001026410609483719</v>
+        <v>0.00102640688419342</v>
       </c>
       <c r="JB48" t="n">
         <v>-0.9999999999999998</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0.004037041217088699</v>
+        <v>0.004037030041217804</v>
       </c>
       <c r="JB49" t="n">
         <v>-0.7199999999999999</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0.0006199963390827179</v>
+        <v>0.0006199739873409271</v>
       </c>
       <c r="JB50" t="n">
         <v>-0.7199999999999999</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0.01639550924301147</v>
+        <v>0.01639551669359207</v>
       </c>
       <c r="JB51" t="n">
         <v>-0.7199999999999999</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0.003963802009820938</v>
+        <v>0.003963794559240341</v>
       </c>
       <c r="JB52" t="n">
         <v>-0.7199999999999999</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0.003281161189079285</v>
+        <v>0.003281183540821075</v>
       </c>
       <c r="JB53" t="n">
         <v>-0.7199999999999999</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>-0.0005563609302043915</v>
+        <v>-0.0005563683807849884</v>
       </c>
       <c r="JB55" t="n">
         <v>-0.9999999999999998</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0.001211550086736679</v>
+        <v>0.001211568713188171</v>
       </c>
       <c r="JB56" t="n">
         <v>-0.9999999999999998</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>-0.001406852155923843</v>
+        <v>-0.001406833529472351</v>
       </c>
       <c r="JB57" t="n">
         <v>-0.9999999999999998</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0.000127844512462616</v>
+        <v>0.0001278221607208252</v>
       </c>
       <c r="JB58" t="n">
         <v>-0.9999999999999998</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0.002312362194061279</v>
+        <v>0.002312399446964264</v>
       </c>
       <c r="JB59" t="n">
         <v>-0.9999999999999998</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>-0.0001480728387832642</v>
+        <v>-0.0001480653882026672</v>
       </c>
       <c r="JB60" t="n">
         <v>-0.9999999999999998</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0.0004664324223995209</v>
+        <v>0.000466424971818924</v>
       </c>
       <c r="JB61" t="n">
         <v>-0.9999999999999998</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0.003625638782978058</v>
+        <v>0.00362565740942955</v>
       </c>
       <c r="JB62" t="n">
         <v>-0.9999999999999998</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>-0.000569462776184082</v>
+        <v>-0.0005694814026355743</v>
       </c>
       <c r="JB63" t="n">
         <v>-0.9999999999999998</v>
@@ -51821,10 +51821,10 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>-0.0007309019565582275</v>
+        <v>-0.000730905681848526</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.1199999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52616,10 +52616,10 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0.002870101481676102</v>
+        <v>0.002870108932256699</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.16</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53414,7 +53414,7 @@
         <v>0.005549635738134384</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.1600000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54206,10 +54206,10 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0.01030046120285988</v>
+        <v>0.01030048727989197</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.1600000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -55001,10 +55001,10 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0.001795757561922073</v>
+        <v>0.001795761287212372</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.16</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>-0.001280978322029114</v>
+        <v>-0.001280955970287323</v>
       </c>
       <c r="JB69" t="n">
         <v>-0.1199999999999999</v>
@@ -56594,7 +56594,7 @@
         <v>-0.0006418265402317047</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.9999999999999998</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>-0.0004691779613494873</v>
+        <v>-0.0004691854119300842</v>
       </c>
       <c r="JB71" t="n">
         <v>-0.9999999999999998</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>-0.0003867931663990021</v>
+        <v>-0.0003867670893669128</v>
       </c>
       <c r="JB72" t="n">
         <v>-0.9999999999999998</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0.0002450048923492432</v>
+        <v>0.0002450011670589447</v>
       </c>
       <c r="JB74" t="n">
         <v>-0.9999999999999998</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>-0.0007973648607730865</v>
+        <v>-0.0007973536849021912</v>
       </c>
       <c r="JB75" t="n">
         <v>-0.9999999999999998</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>-0.0006425864994525909</v>
+        <v>-0.0006425678730010986</v>
       </c>
       <c r="JB76" t="n">
         <v>-0.9999999999999998</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>-0.0002654120326042175</v>
+        <v>-0.000265415757894516</v>
       </c>
       <c r="JB77" t="n">
         <v>-0.9999999999999998</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>-0.0004202574491500854</v>
+        <v>-0.0004202499985694885</v>
       </c>
       <c r="JB78" t="n">
         <v>-0.9999999999999998</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>-0.0003372132778167725</v>
+        <v>-0.0003372207283973694</v>
       </c>
       <c r="JB79" t="n">
         <v>-0.9999999999999998</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>-4.739686846733093e-05</v>
+        <v>-4.740804433822632e-05</v>
       </c>
       <c r="JB80" t="n">
         <v>-0.9999999999999998</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0.0002598240971565247</v>
+        <v>0.0002598166465759277</v>
       </c>
       <c r="JB81" t="n">
         <v>-0.2599999999999998</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0.0002559274435043335</v>
+        <v>0.000255923718214035</v>
       </c>
       <c r="JB82" t="n">
         <v>-0.2599999999999998</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0.00052604079246521</v>
+        <v>0.0005260445177555084</v>
       </c>
       <c r="JB83" t="n">
         <v>-0.2599999999999998</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>-5.774199962615967e-05</v>
+        <v>-5.77196478843689e-05</v>
       </c>
       <c r="JB84" t="n">
         <v>-0.2599999999999998</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>9.954348206520081e-05</v>
+        <v>9.955465793609619e-05</v>
       </c>
       <c r="JB85" t="n">
         <v>-0.2599999999999998</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>-0.0005376860499382019</v>
+        <v>-0.0005376972258090973</v>
       </c>
       <c r="JB86" t="n">
         <v>-0.2599999999999998</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>-4.968792200088501e-05</v>
+        <v>-4.965066909790039e-05</v>
       </c>
       <c r="JB87" t="n">
         <v>-0.2599999999999998</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0.0001666992902755737</v>
+        <v>0.0001666620373725891</v>
       </c>
       <c r="JB89" t="n">
         <v>0.02000000000000007</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0.001778941601514816</v>
+        <v>0.001778926700353622</v>
       </c>
       <c r="JB90" t="n">
         <v>0.02000000000000007</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>-0.0008808821439743042</v>
+        <v>-0.0008808858692646027</v>
       </c>
       <c r="JB91" t="n">
         <v>-0.1199999999999999</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>4.189461469650269e-05</v>
+        <v>4.191696643829346e-05</v>
       </c>
       <c r="JB92" t="n">
         <v>-0.1199999999999999</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>7.845461368560791e-06</v>
+        <v>7.830560207366943e-06</v>
       </c>
       <c r="JB93" t="n">
         <v>-0.9999999999999998</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>-0.0008180961012840271</v>
+        <v>-0.0008181184530258179</v>
       </c>
       <c r="JB94" t="n">
         <v>-0.8599999999999999</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>-0.0001852698624134064</v>
+        <v>-0.0001852773129940033</v>
       </c>
       <c r="JB95" t="n">
         <v>-0.5799999999999998</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0.0004197321832180023</v>
+        <v>0.0004197284579277039</v>
       </c>
       <c r="JB96" t="n">
         <v>0.16</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0.0007252171635627747</v>
+        <v>0.0007252432405948639</v>
       </c>
       <c r="JB97" t="n">
         <v>0.3</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>-0.0001263730227947235</v>
+        <v>-0.0001263543963432312</v>
       </c>
       <c r="JB98" t="n">
         <v>0.5799999999999998</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0.0006348639726638794</v>
+        <v>0.0006348751485347748</v>
       </c>
       <c r="JB100" t="n">
         <v>0.5799999999999998</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0.0005564466118812561</v>
+        <v>0.0005564242601394653</v>
       </c>
       <c r="JB101" t="n">
         <v>0.7199999999999999</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0.0003828033804893494</v>
+        <v>0.0003827884793281555</v>
       </c>
       <c r="JB102" t="n">
         <v>0.8599999999999999</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0.001070313155651093</v>
+        <v>0.001070305705070496</v>
       </c>
       <c r="JB103" t="n">
         <v>0.7199999999999999</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0.0005764737725257874</v>
+        <v>0.0005764812231063843</v>
       </c>
       <c r="JB104" t="n">
         <v>0.7199999999999999</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0.0005468837916851044</v>
+        <v>0.0005468912422657013</v>
       </c>
       <c r="JB105" t="n">
         <v>0.8599999999999999</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0.0007580257952213287</v>
+        <v>0.0007579997181892395</v>
       </c>
       <c r="JB106" t="n">
         <v>0.7199999999999999</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0.0006873011589050293</v>
+        <v>0.0006872937083244324</v>
       </c>
       <c r="JB107" t="n">
         <v>0.7199999999999999</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0.0009616166353225708</v>
+        <v>0.000961601734161377</v>
       </c>
       <c r="JB108" t="n">
         <v>0.8599999999999999</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0.001348711550235748</v>
+        <v>0.001348700374364853</v>
       </c>
       <c r="JB109" t="n">
         <v>0.8599999999999999</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0.001130864024162292</v>
+        <v>0.001130867749452591</v>
       </c>
       <c r="JB110" t="n">
         <v>0.8599999999999999</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0.00135393813252449</v>
+        <v>0.001353941857814789</v>
       </c>
       <c r="JB111" t="n">
         <v>0.9999999999999998</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0.001111045479774475</v>
+        <v>0.001111060380935669</v>
       </c>
       <c r="JB112" t="n">
         <v>0.9999999999999998</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0.001405570656061172</v>
+        <v>0.001405544579029083</v>
       </c>
       <c r="JB113" t="n">
         <v>0.9999999999999998</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0.001741401851177216</v>
+        <v>0.001741379499435425</v>
       </c>
       <c r="JB114" t="n">
         <v>0.9999999999999998</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0.001216951757669449</v>
+        <v>0.001216959208250046</v>
       </c>
       <c r="JB115" t="n">
         <v>0.9999999999999998</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0.001905921846628189</v>
+        <v>0.001905903220176697</v>
       </c>
       <c r="JB116" t="n">
         <v>0.9999999999999998</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0.004883572459220886</v>
+        <v>0.004883579909801483</v>
       </c>
       <c r="JB117" t="n">
         <v>0.9999999999999998</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0.003376524895429611</v>
+        <v>0.003376539796590805</v>
       </c>
       <c r="JB118" t="n">
         <v>0.1199999999999999</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0.01440791413187981</v>
+        <v>0.01440791040658951</v>
       </c>
       <c r="JB119" t="n">
         <v>0.1199999999999999</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0.0008019618690013885</v>
+        <v>0.0008019767701625824</v>
       </c>
       <c r="JB120" t="n">
         <v>-0.1600000000000001</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0.007012870162725449</v>
+        <v>0.007012851536273956</v>
       </c>
       <c r="JB121" t="n">
         <v>-0.4399999999999999</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0.0002719983458518982</v>
+        <v>0.0002719834446907043</v>
       </c>
       <c r="JB122" t="n">
         <v>-0.5799999999999998</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0.0008075572550296783</v>
+        <v>0.0008075609803199768</v>
       </c>
       <c r="JB123" t="n">
         <v>-0.5799999999999998</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0.001770146191120148</v>
+        <v>0.001770172268152237</v>
       </c>
       <c r="JB124" t="n">
         <v>-0.7199999999999999</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0.001041524112224579</v>
+        <v>0.00104152038693428</v>
       </c>
       <c r="JB125" t="n">
         <v>-0.5799999999999996</v>
